--- a/frontend/public/badge_list.xlsx
+++ b/frontend/public/badge_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rishik\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B02CCE-2C6B-4108-815C-309C10CDD7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3A5AE2-218B-4AD7-BD87-17FAA2E58092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1042,7 +1042,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1745,7 +1756,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="1"/>
@@ -2353,7 +2364,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="1"/>
@@ -2993,7 +3004,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="1"/>
@@ -10662,6 +10673,11 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not Available">
+      <formula>NOT(ISERROR(SEARCH("Not Available",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
